--- a/Team-Data/2008-09/1-13-2008-09.xlsx
+++ b/Team-Data/2008-09/1-13-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
         <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>0.595</v>
+        <v>0.611</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q2" t="n">
         <v>0.741</v>
       </c>
       <c r="R2" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="V2" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W2" t="n">
         <v>6.9</v>
@@ -724,43 +791,43 @@
         <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z2" t="n">
         <v>19.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -775,40 +842,40 @@
         <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX2" t="n">
         <v>17</v>
       </c>
-      <c r="AS2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>18</v>
-      </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.769</v>
+        <v>0.775</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -867,64 +934,64 @@
         <v>0.477</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
         <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="O3" t="n">
         <v>21.2</v>
       </c>
       <c r="P3" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
         <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>100.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -933,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>13</v>
@@ -945,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
@@ -960,19 +1027,19 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>29</v>
@@ -984,7 +1051,7 @@
         <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -996,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1025,67 +1092,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.385</v>
+        <v>0.368</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="J4" t="n">
         <v>75.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M4" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="N4" t="n">
         <v>0.352</v>
       </c>
       <c r="O4" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U4" t="n">
         <v>19.9</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
@@ -1094,19 +1161,19 @@
         <v>21.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
@@ -1115,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1136,7 +1203,7 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1148,16 +1215,16 @@
         <v>22</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
@@ -1172,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.405</v>
+        <v>0.421</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,79 +1292,79 @@
         <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L5" t="n">
         <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.801</v>
+        <v>0.798</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S5" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>10</v>
@@ -1306,22 +1373,22 @@
         <v>4</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>6</v>
@@ -1330,13 +1397,13 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
         <v>19</v>
@@ -1348,13 +1415,13 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1392,58 +1459,58 @@
         <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.857</v>
+        <v>0.829</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J6" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.76</v>
+        <v>0.763</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S6" t="n">
         <v>30.8</v>
       </c>
       <c r="T6" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U6" t="n">
         <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8.300000000000001</v>
@@ -1452,37 +1519,37 @@
         <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
         <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
         <v>24</v>
@@ -1491,25 +1558,25 @@
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,25 +1588,25 @@
         <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.579</v>
+        <v>0.595</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,10 +1656,10 @@
         <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
@@ -1604,64 +1671,64 @@
         <v>0.332</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S7" t="n">
         <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB7" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1676,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
         <v>25</v>
@@ -1694,16 +1761,16 @@
         <v>9</v>
       </c>
       <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="n">
         <v>2</v>
       </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1712,10 +1779,10 @@
         <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1753,43 +1820,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J8" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M8" t="n">
         <v>17.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O8" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0.76</v>
@@ -1801,19 +1868,19 @@
         <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
         <v>5.7</v>
@@ -1822,16 +1889,16 @@
         <v>22.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.8</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1840,7 +1907,7 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -1852,7 +1919,7 @@
         <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>14</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
@@ -1888,25 +1955,25 @@
         <v>22</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
         <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.611</v>
+        <v>0.629</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J9" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>4.8</v>
@@ -1968,19 +2035,19 @@
         <v>0.346</v>
       </c>
       <c r="O9" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R9" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T9" t="n">
         <v>40.8</v>
@@ -1992,37 +2059,37 @@
         <v>12.6</v>
       </c>
       <c r="W9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X9" t="n">
         <v>5.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AA9" t="n">
         <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
         <v>19</v>
@@ -2031,7 +2098,7 @@
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
         <v>15</v>
@@ -2040,22 +2107,22 @@
         <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>15</v>
@@ -2064,7 +2131,7 @@
         <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
@@ -2073,16 +2140,16 @@
         <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
         <v>26</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2237,22 +2304,22 @@
         <v>15</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
         <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2261,7 +2328,7 @@
         <v>28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -2299,109 +2366,109 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.615</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="J11" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L11" t="n">
         <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O11" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="P11" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
         <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y11" t="n">
         <v>5.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
         <v>10</v>
@@ -2413,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2422,31 +2489,31 @@
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
         <v>23</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2586,13 +2653,13 @@
         <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
         <v>25</v>
@@ -2604,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
@@ -2613,22 +2680,22 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2777,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
         <v>25</v>
@@ -2792,7 +2859,7 @@
         <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
@@ -2804,10 +2871,10 @@
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -2860,79 +2927,79 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
         <v>18.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O14" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R14" t="n">
         <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2944,10 +3011,10 @@
         <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>14</v>
@@ -2962,16 +3029,16 @@
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2980,25 +3047,25 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.289</v>
+        <v>0.297</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="J15" t="n">
-        <v>77.5</v>
+        <v>77.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M15" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N15" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
         <v>10</v>
@@ -3078,10 +3145,10 @@
         <v>38.2</v>
       </c>
       <c r="U15" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="V15" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W15" t="n">
         <v>7.5</v>
@@ -3090,22 +3157,22 @@
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z15" t="n">
         <v>21.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3117,7 +3184,7 @@
         <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI15" t="n">
         <v>27</v>
@@ -3132,16 +3199,16 @@
         <v>27</v>
       </c>
       <c r="AM15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN15" t="n">
         <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3168,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.541</v>
+        <v>0.528</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.447</v>
       </c>
       <c r="L16" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>17.5</v>
+        <v>17.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.741</v>
+        <v>0.739</v>
       </c>
       <c r="R16" t="n">
         <v>10.7</v>
@@ -3260,13 +3327,13 @@
         <v>40.6</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V16" t="n">
         <v>12.9</v>
       </c>
       <c r="W16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>5.6</v>
@@ -3275,10 +3342,10 @@
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB16" t="n">
         <v>96.59999999999999</v>
@@ -3287,7 +3354,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3299,13 +3366,13 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>12</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>14</v>
       </c>
       <c r="AK16" t="n">
         <v>19</v>
@@ -3314,28 +3381,28 @@
         <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT16" t="n">
         <v>20</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>21</v>
       </c>
       <c r="AU16" t="n">
         <v>26</v>
@@ -3344,16 +3411,16 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
         <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.487</v>
+        <v>0.475</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,10 +3476,10 @@
         <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>5.3</v>
@@ -3421,31 +3488,31 @@
         <v>15.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U17" t="n">
         <v>21.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>6.9</v>
@@ -3457,43 +3524,43 @@
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB17" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
         <v>24</v>
@@ -3502,7 +3569,7 @@
         <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3514,10 +3581,10 @@
         <v>3</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3526,7 +3593,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3640,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.297</v>
+        <v>0.306</v>
       </c>
       <c r="H18" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="n">
         <v>36.4</v>
@@ -3594,37 +3661,37 @@
         <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="P18" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
@@ -3642,7 +3709,7 @@
         <v>22.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB18" t="n">
         <v>97.7</v>
@@ -3651,13 +3718,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
@@ -3678,19 +3745,19 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3702,13 +3769,13 @@
         <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
         <v>23</v>
@@ -3720,7 +3787,7 @@
         <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>-1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3851,16 +3918,16 @@
         <v>24</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
         <v>11</v>
@@ -3878,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
         <v>17</v>
@@ -3890,7 +3957,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
@@ -4030,25 +4097,25 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ20" t="n">
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN20" t="n">
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -4066,7 +4133,7 @@
         <v>28</v>
       </c>
       <c r="AU20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4084,13 +4151,13 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB20" t="n">
         <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
@@ -4212,7 +4279,7 @@
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4221,13 +4288,13 @@
         <v>29</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>26</v>
@@ -4245,16 +4312,16 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4412,10 +4479,10 @@
         <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ22" t="n">
         <v>19</v>
@@ -4430,7 +4497,7 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4483,88 +4550,88 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.795</v>
+        <v>0.789</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.3</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="L23" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.401</v>
+        <v>0.393</v>
       </c>
       <c r="O23" t="n">
         <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.721</v>
+        <v>0.719</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V23" t="n">
         <v>14.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>102</v>
+        <v>101.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
@@ -4576,7 +4643,7 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>21</v>
@@ -4585,16 +4652,16 @@
         <v>8</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4612,13 +4679,13 @@
         <v>7</v>
       </c>
       <c r="AU23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW23" t="n">
         <v>14</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>13</v>
       </c>
       <c r="AX23" t="n">
         <v>5</v>
@@ -4627,13 +4694,13 @@
         <v>4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
@@ -4755,7 +4822,7 @@
         <v>18</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>12</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -4788,13 +4855,13 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
         <v>26</v>
@@ -4806,13 +4873,13 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" t="n">
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0.629</v>
+        <v>0.618</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
@@ -4865,76 +4932,76 @@
         <v>38.5</v>
       </c>
       <c r="J25" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M25" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.399</v>
+        <v>0.394</v>
       </c>
       <c r="O25" t="n">
         <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V25" t="n">
         <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA25" t="n">
         <v>22.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>7</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -4949,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="n">
         <v>6</v>
@@ -4967,7 +5034,7 @@
         <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
         <v>9</v>
@@ -4982,13 +5049,13 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
         <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.639</v>
+        <v>0.622</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
         <v>7.8</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="T26" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4</v>
-      </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,10 +5207,10 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
@@ -5155,7 +5222,7 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>13</v>
@@ -5167,22 +5234,22 @@
         <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
         <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>0.231</v>
+        <v>0.237</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5232,22 +5299,22 @@
         <v>81</v>
       </c>
       <c r="K27" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M27" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="O27" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P27" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="Q27" t="n">
         <v>0.791</v>
@@ -5256,46 +5323,46 @@
         <v>10.3</v>
       </c>
       <c r="S27" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T27" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.1</v>
+        <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
@@ -5304,13 +5371,13 @@
         <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5322,7 +5389,7 @@
         <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>18</v>
@@ -5340,19 +5407,19 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5489,7 +5556,7 @@
         <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5522,7 +5589,7 @@
         <v>24</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5534,10 +5601,10 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>30</v>
@@ -5546,7 +5613,7 @@
         <v>19</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>19</v>
@@ -5662,19 +5729,19 @@
         <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
@@ -5683,10 +5750,10 @@
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5704,19 +5771,19 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
@@ -5874,13 +5941,13 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -5907,10 +5974,10 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
@@ -6017,34 +6084,34 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN31" t="n">
         <v>30</v>
@@ -6062,7 +6129,7 @@
         <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT31" t="n">
         <v>25</v>
@@ -6080,7 +6147,7 @@
         <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-13-2008-09</t>
+          <t>2009-01-13</t>
         </is>
       </c>
     </row>
